--- a/RadixMetricas.xlsx
+++ b/RadixMetricas.xlsx
@@ -1,25 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Estudiantes\Documents\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D43FEE32-D72F-4B71-B72A-D00236E9910C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="4725" yWindow="1785" windowWidth="21600" windowHeight="11385" xr2:uid="{6910775A-F0E6-40A6-A527-3D574CCF3C6B}"/>
+    <workbookView windowWidth="19635" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Radix" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -30,9 +21,6 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -62,13 +50,19 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -76,11 +70,162 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -95,12 +240,198 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor theme="4" tint="0.799981688894314"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -110,14 +441,14 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </left>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
@@ -125,29 +456,271 @@
       <left/>
       <right/>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </right>
       <top style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
       </top>
       <bottom style="thin">
-        <color theme="4" tint="0.39997558519241921"/>
+        <color theme="4" tint="0.399975585192419"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -157,29 +730,1166 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Coma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="K" xfId="3" builtinId="5"/>
+    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
+    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
+    <cellStyle name="Nota" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Salida" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
+    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
+    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
+    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
+    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
+    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
+    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
+    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="es-MX" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Radix</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smooth"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Radix!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Radix!$C$4:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.7324</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.903666</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.124333</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>72.500533</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>780.9164</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Radix!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Radix!$D$4:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.301433</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.719066</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6.7677</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.985366</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>700.618566</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Radix!$B$4:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>40000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Radix!$E$4:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0.1415</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.1691</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.712233</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>67.610566</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>681.6265</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="236824382"/>
+        <c:axId val="982304715"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="236824382"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="es-MX" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="982304715"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="982304715"/>
+        <c:scaling>
+          <c:logBase val="10"/>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="es-MX" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="236824382"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="15000"/>
+              <a:lumOff val="85000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="es-MX" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="es-MX"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10190">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>34925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>815975</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="1144905" y="1727200"/>
+        <a:ext cx="6386195" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -225,7 +1935,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -258,26 +1968,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -310,23 +2003,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -488,28 +2164,23 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F0AB52C-E397-4DA8-9C79-416640EB4C2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A3:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.5666666666667" customWidth="1"/>
+    <col min="2" max="2" width="16.425" customWidth="1"/>
+    <col min="3" max="3" width="16.2833333333333" customWidth="1"/>
+    <col min="4" max="4" width="14.425" customWidth="1"/>
+    <col min="5" max="5" width="15.425" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -526,62 +2197,94 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="4">
         <v>4000</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
+      <c r="C4" s="5">
+        <v>0.7324</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0.301433</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.1415</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="8">
         <v>40000</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
+      <c r="C5" s="9">
+        <v>0.903666</v>
+      </c>
+      <c r="D5" s="9">
+        <v>0.719066</v>
+      </c>
+      <c r="E5" s="10">
+        <v>1.1691</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="4">
         <v>400000</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
+      <c r="C6" s="5">
+        <v>7.124333</v>
+      </c>
+      <c r="D6" s="5">
+        <v>6.7677</v>
+      </c>
+      <c r="E6" s="6">
+        <v>8.712233</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5">
       <c r="A7" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="8">
         <v>4000000</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
+      <c r="C7" s="9">
+        <v>72.500533</v>
+      </c>
+      <c r="D7" s="9">
+        <v>67.985366</v>
+      </c>
+      <c r="E7" s="10">
+        <v>67.610566</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B8" s="4">
         <v>40000000</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="6"/>
+      <c r="C8" s="5">
+        <v>780.9164</v>
+      </c>
+      <c r="D8" s="5">
+        <v>700.618566</v>
+      </c>
+      <c r="E8" s="6">
+        <v>681.6265</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>